--- a/08_tables/q7_twfe_country_correlations_i_WR.xlsx
+++ b/08_tables/q7_twfe_country_correlations_i_WR.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,16 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>std_twfe_WR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>std_twfe_i</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>simple_slope</t>
         </is>
       </c>
@@ -463,7 +473,13 @@
         <v>0.3039842726893356</v>
       </c>
       <c r="D2" t="n">
-        <v>3.324461579653459</v>
+        <v>23.84141911556899</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.180027134042958</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.324461579653462</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +495,13 @@
         <v>0.2226796399325936</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7660858854458255</v>
+        <v>5.036871732513073</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.464077076854049</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7660858854458252</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +517,13 @@
         <v>0.2139789310142512</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5983907828786771</v>
+        <v>4.099917828438966</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.466092157962786</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5983907828786769</v>
       </c>
     </row>
     <row r="5">
@@ -511,6 +539,12 @@
         <v>0.1914446576563747</v>
       </c>
       <c r="D5" t="n">
+        <v>12.66734724525217</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.883554235334497</v>
+      </c>
+      <c r="F5" t="n">
         <v>1.287510553871072</v>
       </c>
     </row>
@@ -527,7 +561,13 @@
         <v>0.1386467554738088</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8753005622675194</v>
+        <v>12.46253219951263</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.974052946994679</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8753005622675193</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +583,13 @@
         <v>0.1147287161564475</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6378179403130153</v>
+        <v>14.11162384810581</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.538355202397322</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6378179403130152</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +605,13 @@
         <v>0.05854856846911453</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9178612072768338</v>
+        <v>15.16997759265883</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9676631550796512</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9178612072768336</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +627,13 @@
         <v>-0.06092761473305857</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.325081220064278</v>
+        <v>12.97165206594206</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.431182642198552</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.3250812200642783</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +649,13 @@
         <v>-0.10864045894489</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5409223371324661</v>
+        <v>6.293579368642915</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.264021291189566</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.5409223371324663</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +671,13 @@
         <v>-0.1843956436203498</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.390877518247976</v>
+        <v>46.88030845688545</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.615628397962685</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-2.390877518247974</v>
       </c>
     </row>
     <row r="12">
@@ -623,6 +693,12 @@
         <v>-0.204881724275418</v>
       </c>
       <c r="D12" t="n">
+        <v>9.445117146899641</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.522409443455344</v>
+      </c>
+      <c r="F12" t="n">
         <v>-1.271098189359646</v>
       </c>
     </row>
@@ -639,7 +715,13 @@
         <v>-0.2616569069760014</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.65027619621425</v>
+        <v>4.73550243749758</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.905462521904596</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.6502761962142497</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +737,13 @@
         <v>-0.3365576363702833</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.132678127071709</v>
+        <v>8.597946471517425</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9237158829327381</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-3.132678127071711</v>
       </c>
     </row>
     <row r="15">
@@ -671,6 +759,12 @@
         <v>-0.4020073820963945</v>
       </c>
       <c r="D15" t="n">
+        <v>7.932583708025634</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.617876248859742</v>
+      </c>
+      <c r="F15" t="n">
         <v>-1.971076101754648</v>
       </c>
     </row>

--- a/08_tables/q7_twfe_country_correlations_i_WR.xlsx
+++ b/08_tables/q7_twfe_country_correlations_i_WR.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,10 +476,10 @@
         <v>23.84141911556899</v>
       </c>
       <c r="E2" t="n">
-        <v>2.180027134042958</v>
+        <v>2.180027134042959</v>
       </c>
       <c r="F2" t="n">
-        <v>3.324461579653462</v>
+        <v>3.32446157965346</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2226796399325936</v>
+        <v>0.2226796399325938</v>
       </c>
       <c r="D3" t="n">
-        <v>5.036871732513073</v>
+        <v>5.036871732513072</v>
       </c>
       <c r="E3" t="n">
         <v>1.464077076854049</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7660858854458252</v>
+        <v>0.7660858854458259</v>
       </c>
     </row>
     <row r="4">
@@ -514,7 +514,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2139789310142512</v>
+        <v>0.2139789310142514</v>
       </c>
       <c r="D4" t="n">
         <v>4.099917828438966</v>
@@ -523,7 +523,7 @@
         <v>1.466092157962786</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5983907828786769</v>
+        <v>0.5983907828786774</v>
       </c>
     </row>
     <row r="5">
@@ -539,10 +539,10 @@
         <v>0.1914446576563747</v>
       </c>
       <c r="D5" t="n">
-        <v>12.66734724525217</v>
+        <v>12.66734724525216</v>
       </c>
       <c r="E5" t="n">
-        <v>1.883554235334497</v>
+        <v>1.883554235334496</v>
       </c>
       <c r="F5" t="n">
         <v>1.287510553871072</v>
@@ -558,7 +558,7 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1386467554738088</v>
+        <v>0.1386467554738087</v>
       </c>
       <c r="D6" t="n">
         <v>12.46253219951263</v>
@@ -567,7 +567,7 @@
         <v>1.974052946994679</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8753005622675193</v>
+        <v>0.8753005622675187</v>
       </c>
     </row>
     <row r="7">
@@ -589,7 +589,7 @@
         <v>2.538355202397322</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6378179403130152</v>
+        <v>0.6378179403130155</v>
       </c>
     </row>
     <row r="8">
@@ -602,7 +602,7 @@
         <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05854856846911453</v>
+        <v>0.05854856846911444</v>
       </c>
       <c r="D8" t="n">
         <v>15.16997759265883</v>
@@ -611,7 +611,7 @@
         <v>0.9676631550796512</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9178612072768336</v>
+        <v>0.9178612072768324</v>
       </c>
     </row>
     <row r="9">
@@ -668,16 +668,16 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1843956436203498</v>
+        <v>-0.1843956436203497</v>
       </c>
       <c r="D11" t="n">
-        <v>46.88030845688545</v>
+        <v>46.88030845688544</v>
       </c>
       <c r="E11" t="n">
-        <v>3.615628397962685</v>
+        <v>3.615628397962684</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.390877518247974</v>
+        <v>-2.390877518247972</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.204881724275418</v>
+        <v>-0.2048817242754179</v>
       </c>
       <c r="D12" t="n">
-        <v>9.445117146899641</v>
+        <v>9.445117146899639</v>
       </c>
       <c r="E12" t="n">
         <v>1.522409443455344</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.271098189359646</v>
+        <v>-1.271098189359645</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         <v>50</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2616569069760014</v>
+        <v>-0.2616569069760013</v>
       </c>
       <c r="D13" t="n">
-        <v>4.73550243749758</v>
+        <v>4.735502437497581</v>
       </c>
       <c r="E13" t="n">
         <v>1.905462521904596</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6502761962142497</v>
+        <v>-0.6502761962142498</v>
       </c>
     </row>
     <row r="14">
@@ -734,13 +734,13 @@
         <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.3365576363702833</v>
+        <v>-0.3365576363702834</v>
       </c>
       <c r="D14" t="n">
         <v>8.597946471517425</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9237158829327381</v>
+        <v>0.9237158829327383</v>
       </c>
       <c r="F14" t="n">
         <v>-3.132678127071711</v>
@@ -756,16 +756,16 @@
         <v>50</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.4020073820963945</v>
+        <v>-0.4020073820963944</v>
       </c>
       <c r="D15" t="n">
-        <v>7.932583708025634</v>
+        <v>7.932583708025636</v>
       </c>
       <c r="E15" t="n">
         <v>1.617876248859742</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.971076101754648</v>
+        <v>-1.971076101754649</v>
       </c>
     </row>
   </sheetData>

--- a/08_tables/q7_twfe_country_correlations_i_WR.xlsx
+++ b/08_tables/q7_twfe_country_correlations_i_WR.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/08_tables/q7_twfe_country_correlations_i_WR.xlsx
+++ b/08_tables/q7_twfe_country_correlations_i_WR.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>correlation</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>std_twfe_WR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>std_twfe_i</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>simple_slope</t>
         </is>
@@ -470,7 +458,7 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3039842726893356</v>
+        <v>0.3039842726893355</v>
       </c>
       <c r="D2" t="n">
         <v>23.84141911556899</v>
@@ -479,7 +467,7 @@
         <v>2.180027134042959</v>
       </c>
       <c r="F2" t="n">
-        <v>3.32446157965346</v>
+        <v>3.324461579653459</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +489,7 @@
         <v>1.464077076854049</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7660858854458259</v>
+        <v>0.7660858854458258</v>
       </c>
     </row>
     <row r="4">
@@ -514,7 +502,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2139789310142514</v>
+        <v>0.2139789310142513</v>
       </c>
       <c r="D4" t="n">
         <v>4.099917828438966</v>
@@ -523,7 +511,7 @@
         <v>1.466092157962786</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5983907828786774</v>
+        <v>0.5983907828786771</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +533,7 @@
         <v>1.883554235334496</v>
       </c>
       <c r="F5" t="n">
-        <v>1.287510553871072</v>
+        <v>1.287510553871073</v>
       </c>
     </row>
     <row r="6">
@@ -580,7 +568,7 @@
         <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1147287161564475</v>
+        <v>0.1147287161564476</v>
       </c>
       <c r="D7" t="n">
         <v>14.11162384810581</v>
@@ -589,7 +577,7 @@
         <v>2.538355202397322</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6378179403130155</v>
+        <v>0.6378179403130158</v>
       </c>
     </row>
     <row r="8">
@@ -602,7 +590,7 @@
         <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05854856846911444</v>
+        <v>0.05854856846911441</v>
       </c>
       <c r="D8" t="n">
         <v>15.16997759265883</v>
@@ -611,7 +599,7 @@
         <v>0.9676631550796512</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9178612072768324</v>
+        <v>0.917861207276832</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +612,7 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.06092761473305857</v>
+        <v>-0.06092761473305861</v>
       </c>
       <c r="D9" t="n">
         <v>12.97165206594206</v>
@@ -633,7 +621,7 @@
         <v>2.431182642198552</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3250812200642783</v>
+        <v>-0.3250812200642786</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +643,7 @@
         <v>1.264021291189566</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5409223371324663</v>
+        <v>-0.540922337132466</v>
       </c>
     </row>
     <row r="11">
@@ -668,7 +656,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1843956436203497</v>
+        <v>-0.1843956436203499</v>
       </c>
       <c r="D11" t="n">
         <v>46.88030845688544</v>
@@ -677,7 +665,7 @@
         <v>3.615628397962684</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.390877518247972</v>
+        <v>-2.390877518247975</v>
       </c>
     </row>
     <row r="12">
@@ -690,7 +678,7 @@
         <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2048817242754179</v>
+        <v>-0.204881724275418</v>
       </c>
       <c r="D12" t="n">
         <v>9.445117146899639</v>
@@ -699,7 +687,7 @@
         <v>1.522409443455344</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.271098189359645</v>
+        <v>-1.271098189359646</v>
       </c>
     </row>
     <row r="13">
@@ -712,7 +700,7 @@
         <v>50</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2616569069760013</v>
+        <v>-0.2616569069760014</v>
       </c>
       <c r="D13" t="n">
         <v>4.735502437497581</v>
@@ -721,7 +709,7 @@
         <v>1.905462521904596</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6502761962142498</v>
+        <v>-0.65027619621425</v>
       </c>
     </row>
     <row r="14">
@@ -734,7 +722,7 @@
         <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.3365576363702834</v>
+        <v>-0.3365576363702831</v>
       </c>
       <c r="D14" t="n">
         <v>8.597946471517425</v>
@@ -743,7 +731,7 @@
         <v>0.9237158829327383</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.132678127071711</v>
+        <v>-3.132678127071708</v>
       </c>
     </row>
     <row r="15">
@@ -765,7 +753,7 @@
         <v>1.617876248859742</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.971076101754649</v>
+        <v>-1.971076101754648</v>
       </c>
     </row>
   </sheetData>
